--- a/manufacturing_pmi_hamcycle_segment_recursive_output/pmi_hamcycle_segment_recursive.xlsx
+++ b/manufacturing_pmi_hamcycle_segment_recursive_output/pmi_hamcycle_segment_recursive.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\16492\Desktop\实习内容\数据处理\data\manufacturing_pmi_hamcycle_segment_recursive_output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\16492\Desktop\实习内容\finance_intership\manufacturing_pmi_hamcycle_segment_recursive_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FF114F-1618-4608-A9A7-19C5E73EE637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE16CD45-8B47-4F6B-9824-EB7D9859AD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -203,7 +203,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -267,7 +267,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -4453,16 +4453,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>140970</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>140970</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
